--- a/public/assets/UpdatedAccountingElements.xlsx
+++ b/public/assets/UpdatedAccountingElements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benso\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40557E7F-9BE8-44AF-B817-C76B7734FC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE13A0BA-2020-47C2-8B50-D5A46CE294E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{922BA294-4DCC-45B5-8780-647AD84B5699}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="5" activeTab="8" xr2:uid="{922BA294-4DCC-45B5-8780-647AD84B5699}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,13 @@
     <sheet name="IS Easy" sheetId="10" r:id="rId6"/>
     <sheet name="IS Medium" sheetId="11" r:id="rId7"/>
     <sheet name="IS Hard" sheetId="12" r:id="rId8"/>
-    <sheet name="Normal Balance Easy" sheetId="14" r:id="rId9"/>
-    <sheet name="Normal Balance Medium" sheetId="15" r:id="rId10"/>
-    <sheet name="Normal Balance Hard" sheetId="16" r:id="rId11"/>
-    <sheet name="A=L+SE - Easy" sheetId="18" r:id="rId12"/>
-    <sheet name="A=L+SE - Medium" sheetId="19" r:id="rId13"/>
-    <sheet name="A=L+SE - Hard" sheetId="20" r:id="rId14"/>
+    <sheet name="Normal Balance - All" sheetId="21" r:id="rId9"/>
+    <sheet name="Normal Balance Easy" sheetId="14" r:id="rId10"/>
+    <sheet name="Normal Balance Medium" sheetId="15" r:id="rId11"/>
+    <sheet name="Normal Balance Hard" sheetId="16" r:id="rId12"/>
+    <sheet name="A=L+SE - Easy" sheetId="18" r:id="rId13"/>
+    <sheet name="A=L+SE - Medium" sheetId="19" r:id="rId14"/>
+    <sheet name="A=L+SE - Hard" sheetId="20" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">All!$A$1:$E$43</definedName>
@@ -37,9 +38,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'IS Easy'!$A$1:$B$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'IS Hard'!$A$1:$B$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'IS Medium'!$A$1:$B$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Normal Balance Easy'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'Normal Balance Hard'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Normal Balance Medium'!#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Normal Balance Easy'!#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'Normal Balance Hard'!#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'Normal Balance Medium'!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="383">
   <si>
     <t>Assets</t>
   </si>
@@ -1667,7 +1668,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E69"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
@@ -2478,12 +2479,408 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F154D7F3-C3D8-4B03-BC6F-5936219A4F16}">
+  <sheetPr codeName="Sheet9">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B57"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:B31">
+    <sortCondition ref="B2:B31"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="59" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8444ABC8-3E90-4153-947D-671A731C5AD5}">
   <sheetPr codeName="Sheet10">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B76"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="42.140625" customWidth="1"/>
@@ -3073,13 +3470,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3178FF7-7A1D-4E9E-B7E2-EC0FF2ACE046}">
   <sheetPr codeName="Sheet11">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B73"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="58.140625" bestFit="1" customWidth="1"/>
@@ -3666,10 +4063,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21BE0DBB-C999-5A44-8548-4898BD2D14AB}">
   <dimension ref="B3:F23"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C3" s="5" t="s">
@@ -4027,10 +4424,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{683674F0-791E-8B43-805E-7A46EA7231CA}">
   <dimension ref="B2:G23"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="87.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -4409,12 +4806,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{191C79E7-2766-A64A-8DC8-E055CFAB5B32}">
   <dimension ref="B2:G23"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="92.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="92.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
@@ -4859,7 +5256,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E69"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41.42578125" bestFit="1" customWidth="1"/>
@@ -5892,7 +6289,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
@@ -6123,7 +6520,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
@@ -6472,7 +6869,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
@@ -6818,7 +7215,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.140625" bestFit="1" customWidth="1"/>
@@ -6997,7 +7394,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B43"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.140625" bestFit="1" customWidth="1"/>
@@ -7278,7 +7675,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B39"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.140625" bestFit="1" customWidth="1"/>
@@ -7549,15 +7946,12 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F154D7F3-C3D8-4B03-BC6F-5936219A4F16}">
-  <sheetPr codeName="Sheet9">
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1924A69-9EA0-4A41-BBB2-9FB56813B04B}">
+  <dimension ref="A1:B127"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7804,143 +8198,675 @@
       <c r="A31" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="B31" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B37" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
         <v>202</v>
       </c>
+      <c r="B56" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>219</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:B31">
-    <sortCondition ref="B2:B31"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="59" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8204,16 +9130,16 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75253D14-554A-4916-839F-E7F866211CA3}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="47b4e388-7a75-40af-8b04-42818f2fdb9b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c997e9c3-07ef-4103-ac9e-c49d1d746bce"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c997e9c3-07ef-4103-ac9e-c49d1d746bce"/>
-    <ds:schemaRef ds:uri="47b4e388-7a75-40af-8b04-42818f2fdb9b"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/public/assets/UpdatedAccountingElements.xlsx
+++ b/public/assets/UpdatedAccountingElements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29406"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tigermailauburn-my.sharepoint.com/personal/mclelaj_auburn_edu/Documents/Teaching/General/Games/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0cd547181c8f633/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="274" documentId="8_{54D263A8-B5FE-8A4A-A7F2-3BAB2E774F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F645D88-5DB5-47F3-9364-61EC83A62E99}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{9F56408F-F42D-4499-9F09-B8DDABF6A78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="30912" windowHeight="16656" firstSheet="12" activeTab="14" xr2:uid="{922BA294-4DCC-45B5-8780-647AD84B5699}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="12" xr2:uid="{922BA294-4DCC-45B5-8780-647AD84B5699}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="399">
   <si>
     <t>Assets</t>
   </si>
@@ -1248,6 +1248,18 @@
   </si>
   <si>
     <t>Jordan-Hare LLP forgets to record the transaction for payment of utilities. It was paid for with cash.</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>J</t>
   </si>
 </sst>
 </file>
@@ -1255,9 +1267,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1282,15 +1294,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1319,6 +1330,11 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1355,10 +1371,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1375,22 +1392,20 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1"/>
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1404,6 +1419,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1727,7 +1746,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E69"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
@@ -1736,7 +1755,7 @@
     <col min="5" max="5" width="44.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1753,7 +1772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -1770,7 +1789,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1787,7 +1806,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -1804,7 +1823,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
@@ -1821,7 +1840,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -1838,7 +1857,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>30</v>
       </c>
@@ -1855,7 +1874,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>35</v>
       </c>
@@ -1872,7 +1891,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>40</v>
       </c>
@@ -1889,7 +1908,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>45</v>
       </c>
@@ -1906,7 +1925,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>50</v>
       </c>
@@ -1923,7 +1942,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>55</v>
       </c>
@@ -1940,7 +1959,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>60</v>
       </c>
@@ -1957,7 +1976,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>65</v>
       </c>
@@ -1971,7 +1990,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>69</v>
       </c>
@@ -1985,7 +2004,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>73</v>
       </c>
@@ -1999,7 +2018,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>77</v>
       </c>
@@ -2013,7 +2032,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>81</v>
       </c>
@@ -2027,7 +2046,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>85</v>
       </c>
@@ -2041,7 +2060,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>89</v>
       </c>
@@ -2052,7 +2071,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>92</v>
       </c>
@@ -2063,7 +2082,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>95</v>
       </c>
@@ -2074,7 +2093,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>98</v>
       </c>
@@ -2085,7 +2104,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>101</v>
       </c>
@@ -2096,7 +2115,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>104</v>
       </c>
@@ -2107,7 +2126,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>107</v>
       </c>
@@ -2118,7 +2137,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>110</v>
       </c>
@@ -2129,7 +2148,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>113</v>
       </c>
@@ -2140,7 +2159,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>116</v>
       </c>
@@ -2151,7 +2170,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>119</v>
       </c>
@@ -2162,7 +2181,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>122</v>
       </c>
@@ -2173,7 +2192,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>125</v>
       </c>
@@ -2184,7 +2203,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>128</v>
       </c>
@@ -2195,7 +2214,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>131</v>
       </c>
@@ -2206,7 +2225,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>134</v>
       </c>
@@ -2217,7 +2236,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>137</v>
       </c>
@@ -2228,7 +2247,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>140</v>
       </c>
@@ -2239,7 +2258,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>143</v>
       </c>
@@ -2250,7 +2269,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>146</v>
       </c>
@@ -2261,7 +2280,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>149</v>
       </c>
@@ -2272,7 +2291,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>152</v>
       </c>
@@ -2283,7 +2302,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>155</v>
       </c>
@@ -2294,7 +2313,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>158</v>
       </c>
@@ -2305,7 +2324,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>161</v>
       </c>
@@ -2316,7 +2335,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>164</v>
       </c>
@@ -2327,7 +2346,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>167</v>
       </c>
@@ -2338,7 +2357,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>170</v>
       </c>
@@ -2349,7 +2368,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>173</v>
       </c>
@@ -2360,7 +2379,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>176</v>
       </c>
@@ -2371,7 +2390,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>179</v>
       </c>
@@ -2382,7 +2401,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>182</v>
       </c>
@@ -2393,7 +2412,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>185</v>
       </c>
@@ -2404,7 +2423,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>188</v>
       </c>
@@ -2415,7 +2434,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>191</v>
       </c>
@@ -2426,7 +2445,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>194</v>
       </c>
@@ -2437,7 +2456,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>197</v>
       </c>
@@ -2448,7 +2467,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>200</v>
       </c>
@@ -2459,7 +2478,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>203</v>
       </c>
@@ -2470,7 +2489,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>206</v>
       </c>
@@ -2478,52 +2497,52 @@
         <v>207</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C60" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C61" s="2" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C62" s="2" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C63" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C64" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="65" spans="3:3">
+    <row r="65" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C65" s="2" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="66" spans="3:3">
+    <row r="66" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C66" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="67" spans="3:3">
+    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C67" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="68" spans="3:3">
+    <row r="68" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C68" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="69" spans="3:3">
+    <row r="69" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C69" s="3" t="s">
         <v>217</v>
       </c>
@@ -2543,13 +2562,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>245</v>
       </c>
@@ -2557,7 +2576,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>247</v>
       </c>
@@ -2565,7 +2584,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -2573,7 +2592,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>248</v>
       </c>
@@ -2581,7 +2600,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>249</v>
       </c>
@@ -2589,7 +2608,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>250</v>
       </c>
@@ -2597,7 +2616,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>40</v>
       </c>
@@ -2605,7 +2624,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
@@ -2613,7 +2632,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>50</v>
       </c>
@@ -2621,7 +2640,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>218</v>
       </c>
@@ -2629,7 +2648,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>251</v>
       </c>
@@ -2637,7 +2656,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>65</v>
       </c>
@@ -2645,7 +2664,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>39</v>
       </c>
@@ -2653,7 +2672,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>252</v>
       </c>
@@ -2661,7 +2680,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>253</v>
       </c>
@@ -2669,7 +2688,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>85</v>
       </c>
@@ -2677,7 +2696,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>254</v>
       </c>
@@ -2685,7 +2704,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>95</v>
       </c>
@@ -2693,7 +2712,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>255</v>
       </c>
@@ -2701,7 +2720,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>98</v>
       </c>
@@ -2709,7 +2728,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>257</v>
       </c>
@@ -2717,7 +2736,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>258</v>
       </c>
@@ -2725,7 +2744,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>101</v>
       </c>
@@ -2733,7 +2752,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>104</v>
       </c>
@@ -2741,7 +2760,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>110</v>
       </c>
@@ -2749,7 +2768,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>122</v>
       </c>
@@ -2757,7 +2776,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>128</v>
       </c>
@@ -2765,7 +2784,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>261</v>
       </c>
@@ -2773,7 +2792,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>263</v>
       </c>
@@ -2781,7 +2800,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>264</v>
       </c>
@@ -2789,137 +2808,137 @@
         <v>198</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>279</v>
       </c>
@@ -2939,13 +2958,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B76"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="42.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>308</v>
       </c>
@@ -2953,7 +2972,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>247</v>
       </c>
@@ -2961,7 +2980,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -2969,7 +2988,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>248</v>
       </c>
@@ -2977,7 +2996,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>280</v>
       </c>
@@ -2985,7 +3004,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>281</v>
       </c>
@@ -2993,7 +3012,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
@@ -3001,7 +3020,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>282</v>
       </c>
@@ -3009,7 +3028,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>40</v>
       </c>
@@ -3017,7 +3036,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>45</v>
       </c>
@@ -3025,7 +3044,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>60</v>
       </c>
@@ -3033,7 +3052,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>284</v>
       </c>
@@ -3041,7 +3060,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
@@ -3049,7 +3068,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>285</v>
       </c>
@@ -3057,7 +3076,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>73</v>
       </c>
@@ -3065,7 +3084,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>67</v>
       </c>
@@ -3073,7 +3092,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>71</v>
       </c>
@@ -3081,7 +3100,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>77</v>
       </c>
@@ -3089,7 +3108,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>286</v>
       </c>
@@ -3097,7 +3116,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>287</v>
       </c>
@@ -3105,7 +3124,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
@@ -3113,7 +3132,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>85</v>
       </c>
@@ -3121,7 +3140,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>288</v>
       </c>
@@ -3129,7 +3148,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>89</v>
       </c>
@@ -3137,7 +3156,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>92</v>
       </c>
@@ -3145,7 +3164,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>98</v>
       </c>
@@ -3153,7 +3172,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>289</v>
       </c>
@@ -3161,7 +3180,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>257</v>
       </c>
@@ -3169,7 +3188,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>258</v>
       </c>
@@ -3177,7 +3196,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>101</v>
       </c>
@@ -3185,7 +3204,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>104</v>
       </c>
@@ -3193,7 +3212,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>110</v>
       </c>
@@ -3201,7 +3220,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>290</v>
       </c>
@@ -3209,7 +3228,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>122</v>
       </c>
@@ -3217,7 +3236,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>291</v>
       </c>
@@ -3225,7 +3244,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>127</v>
       </c>
@@ -3233,7 +3252,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>130</v>
       </c>
@@ -3241,7 +3260,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>133</v>
       </c>
@@ -3249,7 +3268,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>292</v>
       </c>
@@ -3257,7 +3276,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>134</v>
       </c>
@@ -3265,7 +3284,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>140</v>
       </c>
@@ -3273,7 +3292,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>143</v>
       </c>
@@ -3281,7 +3300,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>294</v>
       </c>
@@ -3289,7 +3308,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>146</v>
       </c>
@@ -3297,7 +3316,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>295</v>
       </c>
@@ -3305,7 +3324,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>149</v>
       </c>
@@ -3313,7 +3332,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>152</v>
       </c>
@@ -3321,7 +3340,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>155</v>
       </c>
@@ -3329,7 +3348,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>296</v>
       </c>
@@ -3337,7 +3356,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>297</v>
       </c>
@@ -3345,7 +3364,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>173</v>
       </c>
@@ -3353,7 +3372,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>298</v>
       </c>
@@ -3361,7 +3380,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>269</v>
       </c>
@@ -3369,7 +3388,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>299</v>
       </c>
@@ -3377,7 +3396,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>270</v>
       </c>
@@ -3385,7 +3404,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>80</v>
       </c>
@@ -3393,7 +3412,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>84</v>
       </c>
@@ -3401,7 +3420,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>179</v>
       </c>
@@ -3409,7 +3428,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>300</v>
       </c>
@@ -3417,7 +3436,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>301</v>
       </c>
@@ -3425,7 +3444,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>182</v>
       </c>
@@ -3433,7 +3452,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>271</v>
       </c>
@@ -3441,7 +3460,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>185</v>
       </c>
@@ -3449,7 +3468,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>302</v>
       </c>
@@ -3457,7 +3476,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>303</v>
       </c>
@@ -3465,57 +3484,57 @@
         <v>204</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>206</v>
       </c>
@@ -3535,13 +3554,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B73"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="58.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>308</v>
       </c>
@@ -3549,7 +3568,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>282</v>
       </c>
@@ -3557,7 +3576,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>92</v>
       </c>
@@ -3565,7 +3584,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>100</v>
       </c>
@@ -3573,7 +3592,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>247</v>
       </c>
@@ -3581,7 +3600,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -3589,7 +3608,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>137</v>
       </c>
@@ -3597,7 +3616,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>127</v>
       </c>
@@ -3605,7 +3624,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>130</v>
       </c>
@@ -3613,7 +3632,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>133</v>
       </c>
@@ -3621,7 +3640,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>274</v>
       </c>
@@ -3629,7 +3648,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>9</v>
       </c>
@@ -3637,7 +3656,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>20</v>
       </c>
@@ -3645,7 +3664,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>248</v>
       </c>
@@ -3653,7 +3672,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
@@ -3661,7 +3680,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>45</v>
       </c>
@@ -3669,7 +3688,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>303</v>
       </c>
@@ -3677,7 +3696,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>131</v>
       </c>
@@ -3685,7 +3704,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>110</v>
       </c>
@@ -3693,7 +3712,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>116</v>
       </c>
@@ -3701,7 +3720,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>290</v>
       </c>
@@ -3709,7 +3728,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>101</v>
       </c>
@@ -3717,7 +3736,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>143</v>
       </c>
@@ -3725,7 +3744,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>191</v>
       </c>
@@ -3733,7 +3752,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>169</v>
       </c>
@@ -3741,7 +3760,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>298</v>
       </c>
@@ -3749,7 +3768,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>269</v>
       </c>
@@ -3757,7 +3776,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>307</v>
       </c>
@@ -3765,7 +3784,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>197</v>
       </c>
@@ -3773,7 +3792,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>55</v>
       </c>
@@ -3781,7 +3800,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>148</v>
       </c>
@@ -3789,7 +3808,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>284</v>
       </c>
@@ -3797,7 +3816,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>146</v>
       </c>
@@ -3805,7 +3824,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>285</v>
       </c>
@@ -3813,7 +3832,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>113</v>
       </c>
@@ -3821,7 +3840,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>257</v>
       </c>
@@ -3829,7 +3848,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>73</v>
       </c>
@@ -3837,7 +3856,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>194</v>
       </c>
@@ -3845,7 +3864,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>258</v>
       </c>
@@ -3853,7 +3872,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>67</v>
       </c>
@@ -3861,7 +3880,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>263</v>
       </c>
@@ -3869,7 +3888,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>280</v>
       </c>
@@ -3877,7 +3896,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>27</v>
       </c>
@@ -3885,7 +3904,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>71</v>
       </c>
@@ -3893,7 +3912,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>124</v>
       </c>
@@ -3901,7 +3920,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>211</v>
       </c>
@@ -3909,7 +3928,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>305</v>
       </c>
@@ -3917,7 +3936,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>270</v>
       </c>
@@ -3925,7 +3944,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>77</v>
       </c>
@@ -3933,7 +3952,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>155</v>
       </c>
@@ -3941,7 +3960,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>81</v>
       </c>
@@ -3949,7 +3968,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>292</v>
       </c>
@@ -3957,7 +3976,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>119</v>
       </c>
@@ -3965,7 +3984,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>287</v>
       </c>
@@ -3973,7 +3992,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>273</v>
       </c>
@@ -3981,7 +4000,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>70</v>
       </c>
@@ -3989,7 +4008,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>182</v>
       </c>
@@ -3997,7 +4016,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>84</v>
       </c>
@@ -4005,7 +4024,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>161</v>
       </c>
@@ -4013,7 +4032,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>74</v>
       </c>
@@ -4021,7 +4040,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>80</v>
       </c>
@@ -4029,7 +4048,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>170</v>
       </c>
@@ -4037,7 +4056,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>107</v>
       </c>
@@ -4045,7 +4064,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>98</v>
       </c>
@@ -4053,7 +4072,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>39</v>
       </c>
@@ -4061,7 +4080,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>140</v>
       </c>
@@ -4069,7 +4088,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>299</v>
       </c>
@@ -4077,7 +4096,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>252</v>
       </c>
@@ -4085,7 +4104,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>288</v>
       </c>
@@ -4093,22 +4112,22 @@
         <v>204</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>276</v>
       </c>
@@ -4124,14 +4143,14 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21BE0DBB-C999-5A44-8548-4898BD2D14AB}">
-  <dimension ref="A3:J27"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <dimension ref="A3:K27"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
     <col min="6" max="6" width="111.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="15">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C3" s="5" t="s">
         <v>310</v>
       </c>
@@ -4150,11 +4169,11 @@
       <c r="I3" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="11" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="15">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1</v>
       </c>
@@ -4173,17 +4192,20 @@
       <c r="G4">
         <v>200</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="15">
         <v>300</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4">
         <v>500</v>
       </c>
       <c r="J4">
         <v>700</v>
       </c>
-    </row>
-    <row r="5" spans="2:10" ht="15">
+      <c r="K4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>2</v>
       </c>
@@ -4202,17 +4224,20 @@
       <c r="G5">
         <v>500</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="14">
         <v>1000</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="16">
         <v>1500</v>
       </c>
-      <c r="J5" s="21">
+      <c r="J5" s="14">
         <v>2000</v>
       </c>
-    </row>
-    <row r="6" spans="2:10" ht="15">
+      <c r="K5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>3</v>
       </c>
@@ -4231,7 +4256,7 @@
       <c r="G6">
         <v>400</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="15">
         <v>500</v>
       </c>
       <c r="I6">
@@ -4240,8 +4265,11 @@
       <c r="J6">
         <v>1300</v>
       </c>
-    </row>
-    <row r="7" spans="2:10" ht="15">
+      <c r="K6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>4</v>
       </c>
@@ -4257,20 +4285,23 @@
       <c r="F7" t="s">
         <v>320</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="15">
         <v>500</v>
       </c>
       <c r="H7">
         <v>800</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="14">
         <v>1200</v>
       </c>
-      <c r="J7" s="19">
+      <c r="J7" s="14">
         <v>1900</v>
       </c>
-    </row>
-    <row r="8" spans="2:10" ht="15">
+      <c r="K7" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>5</v>
       </c>
@@ -4289,17 +4320,20 @@
       <c r="G8">
         <v>250</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="15">
         <v>500</v>
       </c>
       <c r="I8">
         <v>750</v>
       </c>
-      <c r="J8" s="19">
+      <c r="J8" s="14">
         <v>1000</v>
       </c>
-    </row>
-    <row r="9" spans="2:10" ht="15">
+      <c r="K8" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>6</v>
       </c>
@@ -4315,20 +4349,23 @@
       <c r="F9" t="s">
         <v>322</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="15">
         <v>600</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="14">
         <v>1200</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="14">
         <v>1800</v>
       </c>
-      <c r="J9" s="19">
+      <c r="J9" s="14">
         <v>3000</v>
       </c>
-    </row>
-    <row r="10" spans="2:10" ht="15">
+      <c r="K9" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>7</v>
       </c>
@@ -4344,20 +4381,23 @@
       <c r="F10" t="s">
         <v>323</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="15">
         <v>400</v>
       </c>
       <c r="H10">
         <v>600</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="14">
         <v>1000</v>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="14">
         <v>1600</v>
       </c>
-    </row>
-    <row r="11" spans="2:10" ht="15">
+      <c r="K10" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>8</v>
       </c>
@@ -4376,17 +4416,20 @@
       <c r="G11">
         <v>800</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="16">
         <v>1400</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="14">
         <v>2200</v>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="14">
         <v>3000</v>
       </c>
-    </row>
-    <row r="12" spans="2:10" ht="15">
+      <c r="K11" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>9</v>
       </c>
@@ -4402,20 +4445,23 @@
       <c r="F12" t="s">
         <v>325</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="15">
         <v>500</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="14">
         <v>1100</v>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="14">
         <v>1600</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="14">
         <v>2700</v>
       </c>
-    </row>
-    <row r="13" spans="2:10" ht="15">
+      <c r="K12" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>10</v>
       </c>
@@ -4437,14 +4483,17 @@
       <c r="H13">
         <v>700</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="14">
         <v>1000</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J13" s="16">
         <v>1300</v>
       </c>
-    </row>
-    <row r="14" spans="2:10" ht="15">
+      <c r="K13" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>11</v>
       </c>
@@ -4460,7 +4509,7 @@
       <c r="F14" t="s">
         <v>327</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="15">
         <v>100</v>
       </c>
       <c r="H14">
@@ -4469,11 +4518,14 @@
       <c r="I14">
         <v>600</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="14">
         <v>1100</v>
       </c>
-    </row>
-    <row r="15" spans="2:10" ht="15">
+      <c r="K14" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>12</v>
       </c>
@@ -4489,20 +4541,23 @@
       <c r="F15" t="s">
         <v>328</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="15">
         <v>500</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="14">
         <v>1500</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="14">
         <v>2000</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="14">
         <v>3500</v>
       </c>
-    </row>
-    <row r="16" spans="2:10" ht="15">
+      <c r="K15" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>13</v>
       </c>
@@ -4518,20 +4573,23 @@
       <c r="F16" t="s">
         <v>329</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="15">
         <v>800</v>
       </c>
       <c r="H16">
         <v>900</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="14">
         <v>1700</v>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="14">
         <v>2600</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="15">
+      <c r="K16" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>14</v>
       </c>
@@ -4547,20 +4605,23 @@
       <c r="F17" t="s">
         <v>330</v>
       </c>
-      <c r="G17" s="18">
+      <c r="G17">
         <v>600</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="15">
         <v>800</v>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="14">
         <v>1400</v>
       </c>
-      <c r="J17" s="19">
+      <c r="J17" s="14">
         <v>2000</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="15">
+      <c r="K17" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>15</v>
       </c>
@@ -4576,20 +4637,23 @@
       <c r="F18" t="s">
         <v>331</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="14">
         <v>1000</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="16">
         <v>1500</v>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="14">
         <v>2500</v>
       </c>
-      <c r="J18" s="19">
+      <c r="J18" s="14">
         <v>3500</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="15">
+      <c r="K18" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>16</v>
       </c>
@@ -4605,20 +4669,23 @@
       <c r="F19" t="s">
         <v>332</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="15">
         <v>600</v>
       </c>
       <c r="H19">
         <v>900</v>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="14">
         <v>1500</v>
       </c>
-      <c r="J19" s="19">
+      <c r="J19" s="14">
         <v>2400</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="15">
+      <c r="K19" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>17</v>
       </c>
@@ -4637,17 +4704,20 @@
       <c r="G20">
         <v>500</v>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="14">
         <v>1000</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="14">
         <v>2000</v>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="16">
         <v>4000</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="15">
+      <c r="K20" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>18</v>
       </c>
@@ -4663,20 +4733,23 @@
       <c r="F21" t="s">
         <v>334</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="13">
         <v>250</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="17">
         <v>500</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="13">
         <v>1000</v>
       </c>
-      <c r="J21" s="15">
+      <c r="J21" s="13">
         <v>1500</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="15">
+      <c r="K21" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>19</v>
       </c>
@@ -4692,20 +4765,23 @@
       <c r="F22" t="s">
         <v>335</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="14">
         <v>1000</v>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="14">
         <v>1500</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="14">
         <v>2500</v>
       </c>
-      <c r="J22" s="20">
+      <c r="J22" s="16">
         <v>4000</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="15">
+      <c r="K22" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>20</v>
       </c>
@@ -4724,41 +4800,44 @@
       <c r="G23">
         <v>250</v>
       </c>
-      <c r="H23" s="20">
+      <c r="H23" s="16">
         <v>1250</v>
       </c>
-      <c r="I23" s="19">
+      <c r="I23" s="14">
         <v>1500</v>
       </c>
-      <c r="J23" s="19">
+      <c r="J23" s="14">
         <v>1750</v>
       </c>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="K23" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>337</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="12" t="s">
         <v>338</v>
       </c>
       <c r="C26">
         <v>200</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="12" t="s">
         <v>339</v>
       </c>
       <c r="E26">
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
-      <c r="B27" s="13" t="s">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="12" t="s">
         <v>340</v>
       </c>
       <c r="C27">
         <v>300</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="12" t="s">
         <v>341</v>
       </c>
       <c r="E27">
@@ -4773,21 +4852,21 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{683674F0-791E-8B43-805E-7A46EA7231CA}">
   <dimension ref="B2:J23"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="119" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
-      <c r="C2" s="12" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C2" s="18" t="s">
         <v>342</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-    </row>
-    <row r="3" spans="2:10">
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
         <v>343</v>
       </c>
@@ -4813,7 +4892,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="6">
         <v>1</v>
       </c>
@@ -4834,7 +4913,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="6">
         <v>2</v>
       </c>
@@ -4850,7 +4929,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="6">
         <v>3</v>
       </c>
@@ -4868,7 +4947,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="6">
         <v>4</v>
       </c>
@@ -4884,7 +4963,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="6">
         <v>5</v>
       </c>
@@ -4902,7 +4981,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="6">
         <v>6</v>
       </c>
@@ -4920,7 +4999,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="6">
         <v>7</v>
       </c>
@@ -4936,7 +5015,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="6">
         <v>8</v>
       </c>
@@ -4954,7 +5033,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="6">
         <v>9</v>
       </c>
@@ -4970,7 +5049,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="6">
         <v>10</v>
       </c>
@@ -4986,7 +5065,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="6">
         <v>11</v>
       </c>
@@ -5002,7 +5081,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="6">
         <v>12</v>
       </c>
@@ -5018,7 +5097,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="6">
         <v>13</v>
       </c>
@@ -5036,7 +5115,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="6">
         <v>14</v>
       </c>
@@ -5054,7 +5133,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="6">
         <v>15</v>
       </c>
@@ -5072,7 +5151,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="6">
         <v>16</v>
       </c>
@@ -5090,7 +5169,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="6">
         <v>17</v>
       </c>
@@ -5108,7 +5187,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="6">
         <v>18</v>
       </c>
@@ -5126,7 +5205,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="6">
         <v>19</v>
       </c>
@@ -5138,7 +5217,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="6">
         <v>20</v>
       </c>
@@ -5165,21 +5244,21 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{191C79E7-2766-A64A-8DC8-E055CFAB5B32}">
   <dimension ref="B2:G23"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="150.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7">
-      <c r="C2" s="12" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C2" s="18" t="s">
         <v>342</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-    </row>
-    <row r="3" spans="2:7">
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
         <v>343</v>
       </c>
@@ -5199,7 +5278,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="6">
         <v>1</v>
       </c>
@@ -5219,7 +5298,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="6">
         <v>2</v>
       </c>
@@ -5239,7 +5318,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="6">
         <v>3</v>
       </c>
@@ -5259,7 +5338,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="6">
         <v>4</v>
       </c>
@@ -5279,7 +5358,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="6">
         <v>5</v>
       </c>
@@ -5299,7 +5378,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="6">
         <v>6</v>
       </c>
@@ -5319,7 +5398,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="6">
         <v>7</v>
       </c>
@@ -5339,7 +5418,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="11" spans="2:7">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="6">
         <v>8</v>
       </c>
@@ -5359,7 +5438,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="6">
         <v>9</v>
       </c>
@@ -5379,7 +5458,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="13" spans="2:7">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="6">
         <v>10</v>
       </c>
@@ -5399,7 +5478,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="14" spans="2:7">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="6">
         <v>11</v>
       </c>
@@ -5419,7 +5498,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="15" spans="2:7">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="6">
         <v>12</v>
       </c>
@@ -5439,7 +5518,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="16" spans="2:7">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="6">
         <v>13</v>
       </c>
@@ -5459,7 +5538,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="6">
         <v>14</v>
       </c>
@@ -5479,7 +5558,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="6">
         <v>15</v>
       </c>
@@ -5499,7 +5578,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="6">
         <v>16</v>
       </c>
@@ -5519,7 +5598,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="6">
         <v>17</v>
       </c>
@@ -5539,7 +5618,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="6">
         <v>18</v>
       </c>
@@ -5559,7 +5638,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="6">
         <v>19</v>
       </c>
@@ -5579,7 +5658,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="6">
         <v>20</v>
       </c>
@@ -5613,7 +5692,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E69"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41.42578125" bestFit="1" customWidth="1"/>
@@ -5622,7 +5701,7 @@
     <col min="5" max="5" width="53" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5639,7 +5718,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="str">
         <f>_xlfn.CONCAT(All!A2, " - Assets")</f>
         <v>Accounts Receivable - Assets</v>
@@ -5661,7 +5740,7 @@
         <v>Accumulated Other Comprehenseive Income - Stockholder's Equity</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="str">
         <f>_xlfn.CONCAT(All!A3, " - Assets")</f>
         <v>Accumulated Depletion - Assets</v>
@@ -5683,7 +5762,7 @@
         <v>Accumulated Profits - Stockholder's Equity</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="str">
         <f>_xlfn.CONCAT(All!A4, " - Assets")</f>
         <v>Accumulated Depreciation - Assets</v>
@@ -5705,7 +5784,7 @@
         <v>Additional Paid in Capital - Common Stock - Stockholder's Equity</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="str">
         <f>_xlfn.CONCAT(All!A5, " - Assets")</f>
         <v>Advances to Officers, Directors, and Employees - Assets</v>
@@ -5727,7 +5806,7 @@
         <v>Additional Paid in Capital - Preferred Stock - Stockholder's Equity</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="str">
         <f>_xlfn.CONCAT(All!A6, " - Assets")</f>
         <v>Allowance for Doubtful Accounts - Assets</v>
@@ -5749,7 +5828,7 @@
         <v>Additional Paid in Capital - Treasury Stock - Stockholder's Equity</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="str">
         <f>_xlfn.CONCAT(All!A7, " - Assets")</f>
         <v>Allowance to Adjust Available-for-Sale Securities to Market - Assets</v>
@@ -5771,7 +5850,7 @@
         <v>Common Stock - Stockholder's Equity</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="str">
         <f>_xlfn.CONCAT(All!A8, " - Assets")</f>
         <v>Allowance to Adjust Trading Securities to Market - Assets</v>
@@ -5793,7 +5872,7 @@
         <v>Dividends Paid - Stockholder's Equity</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="str">
         <f>_xlfn.CONCAT(All!A9, " - Assets")</f>
         <v>Buildings - Assets</v>
@@ -5815,7 +5894,7 @@
         <v>Preferred Stock - Stockholder's Equity</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="str">
         <f>_xlfn.CONCAT(All!A10, " - Assets")</f>
         <v>Cash - Assets</v>
@@ -5837,7 +5916,7 @@
         <v>Retained Earnings - Stockholder's Equity</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <f>_xlfn.CONCAT(All!A11, " - Assets")</f>
         <v>Cash Equivalents - Assets</v>
@@ -5859,7 +5938,7 @@
         <v>Treasury Stock - Stockholder's Equity</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="str">
         <f>_xlfn.CONCAT(All!A12, " - Assets")</f>
         <v>Certificates of Deposit - Assets</v>
@@ -5881,7 +5960,7 @@
         <v>Unrealized Gain on Available for Sale Securities - Stockholder's Equity</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="str">
         <f>_xlfn.CONCAT(All!A13, " - Assets")</f>
         <v>Checking Accounts - Assets</v>
@@ -5903,7 +5982,7 @@
         <v>Unrealized Loss on Available for Sale Securities - Stockholder's Equity</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="str">
         <f>_xlfn.CONCAT(All!A14, " - Assets")</f>
         <v>Computer Equipment - Assets</v>
@@ -5921,7 +6000,7 @@
         <v>Rent Receipts - Revenue</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="str">
         <f>_xlfn.CONCAT(All!A15, " - Assets")</f>
         <v>Computer Hardware - Assets</v>
@@ -5939,7 +6018,7 @@
         <v>Royalty Income - Revenue</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="str">
         <f>_xlfn.CONCAT(All!A16, " - Assets")</f>
         <v>Copyright - Assets</v>
@@ -5957,7 +6036,7 @@
         <v>Sales - Revenue</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="str">
         <f>_xlfn.CONCAT(All!A17, " - Assets")</f>
         <v>Customer Lists - Assets</v>
@@ -5975,7 +6054,7 @@
         <v>Sales Discounts - Revenue</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="str">
         <f>_xlfn.CONCAT(All!A18, " - Assets")</f>
         <v>Deferred Tax Assets - Assets</v>
@@ -5993,7 +6072,7 @@
         <v>Sales Returns and Allowances - Revenue</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="str">
         <f>_xlfn.CONCAT(All!A19, " - Assets")</f>
         <v>Equipment - Assets</v>
@@ -6011,7 +6090,7 @@
         <v>Unrealized Gain on Trading Securities - Revenue</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="str">
         <f>_xlfn.CONCAT(All!A20, " - Assets")</f>
         <v>Finished Goods Inventory - Assets</v>
@@ -6025,7 +6104,7 @@
         <v>Entertainment Costs - Expense</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="str">
         <f>_xlfn.CONCAT(All!A21, " - Assets")</f>
         <v>Franchise - Assets</v>
@@ -6039,7 +6118,7 @@
         <v>Wages Costs - Expense</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="str">
         <f>_xlfn.CONCAT(All!A22, " - Assets")</f>
         <v>Furniture - Assets</v>
@@ -6053,7 +6132,7 @@
         <v>Equipment Rental Fees - Expense</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="str">
         <f>_xlfn.CONCAT(All!A23, " - Assets")</f>
         <v>Goodwill - Assets</v>
@@ -6067,7 +6146,7 @@
         <v>Federal Taxes Paid - Expense</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="str">
         <f>_xlfn.CONCAT(All!A24, " - Assets")</f>
         <v>Interest Receivable - Assets</v>
@@ -6081,7 +6160,7 @@
         <v>Fines and Penalties - Expense</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="str">
         <f>_xlfn.CONCAT(All!A25, " - Assets")</f>
         <v>Inventory - Assets</v>
@@ -6095,7 +6174,7 @@
         <v>Foreign Exchange Losses - Expense</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="str">
         <f>_xlfn.CONCAT(All!A26, " - Assets")</f>
         <v>Investment in Subsidiary - Assets</v>
@@ -6109,7 +6188,7 @@
         <v>Gas Costs - Expense</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="str">
         <f>_xlfn.CONCAT(All!A27, " - Assets")</f>
         <v>Investments - Assets</v>
@@ -6123,7 +6202,7 @@
         <v>Income Taxes Costs - Expense</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="str">
         <f>_xlfn.CONCAT(All!A28, " - Assets")</f>
         <v>Investments-Available-for-Sale Securities - Assets</v>
@@ -6137,7 +6216,7 @@
         <v>Insurance Costs - Expense</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="str">
         <f>_xlfn.CONCAT(All!A29, " - Assets")</f>
         <v>Investments-Equity Method - Assets</v>
@@ -6151,7 +6230,7 @@
         <v>Interest Costs - Expense</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="str">
         <f>_xlfn.CONCAT(All!A30, " - Assets")</f>
         <v>Investments-Trading Securities - Assets</v>
@@ -6165,7 +6244,7 @@
         <v>IT Costs - Expense</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="str">
         <f>_xlfn.CONCAT(All!A31, " - Assets")</f>
         <v>Land - Assets</v>
@@ -6179,7 +6258,7 @@
         <v>Legal Fees - Expense</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="str">
         <f>_xlfn.CONCAT(All!A32, " - Assets")</f>
         <v>Leased Assets - Assets</v>
@@ -6193,7 +6272,7 @@
         <v>License Fees and Taxes - Expense</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="str">
         <f>_xlfn.CONCAT(All!A33, " - Assets")</f>
         <v>Leasehold Improvements - Assets</v>
@@ -6207,7 +6286,7 @@
         <v>Loss from Impairment - Expense</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="str">
         <f>_xlfn.CONCAT(All!A34, " - Assets")</f>
         <v>Marketable Securities - Assets</v>
@@ -6221,7 +6300,7 @@
         <v>Loss on Disposal of Property,Plant, &amp; Equipment - Expense</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="str">
         <f>_xlfn.CONCAT(All!A35, " - Assets")</f>
         <v>Money Market Accounts - Assets</v>
@@ -6235,7 +6314,7 @@
         <v>Loss on Sale of Intangibles - Expense</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="str">
         <f>_xlfn.CONCAT(All!A36, " - Assets")</f>
         <v>Natural Resources - Assets</v>
@@ -6249,7 +6328,7 @@
         <v>Loss on Sale of Investments - Expense</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="str">
         <f>_xlfn.CONCAT(All!A37, " - Assets")</f>
         <v>Notes Receivable - Assets</v>
@@ -6263,7 +6342,7 @@
         <v>Meals Costs - Expense</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="str">
         <f>_xlfn.CONCAT(All!A38, " - Assets")</f>
         <v>Office Equipment - Assets</v>
@@ -6277,7 +6356,7 @@
         <v>Medicare Taxes Cost - Expense</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="str">
         <f>_xlfn.CONCAT(All!A39, " - Assets")</f>
         <v>Patents - Assets</v>
@@ -6291,7 +6370,7 @@
         <v>Miscellaneous Costs - Expense</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="str">
         <f>_xlfn.CONCAT(All!A40, " - Assets")</f>
         <v>Petty Cash - Assets</v>
@@ -6305,7 +6384,7 @@
         <v>Office Rent Fees - Expense</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="str">
         <f>_xlfn.CONCAT(All!A41, " - Assets")</f>
         <v>Prepaid Advertising - Assets</v>
@@ -6319,7 +6398,7 @@
         <v>Organizational Costs - Expense</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="str">
         <f>_xlfn.CONCAT(All!A42, " - Assets")</f>
         <v>Prepaid Insurance - Assets</v>
@@ -6333,7 +6412,7 @@
         <v>Other Costs - Expense</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="str">
         <f>_xlfn.CONCAT(All!A43, " - Assets")</f>
         <v>Prepaid Office Supplies - Assets</v>
@@ -6347,7 +6426,7 @@
         <v>Penalties and Fines - Expense</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="str">
         <f>_xlfn.CONCAT(All!A44, " - Assets")</f>
         <v>Prepaid Rent - Assets</v>
@@ -6361,7 +6440,7 @@
         <v>Postage Costs - Expense</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="e">
         <f>_xlfn.CONCAT(All!#REF!, " - Assets")</f>
         <v>#REF!</v>
@@ -6375,7 +6454,7 @@
         <v>Warranty Costs - Expense</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="str">
         <f>_xlfn.CONCAT(All!A45, " - Assets")</f>
         <v>Prepaid Repairs &amp; Maintenance - Assets</v>
@@ -6389,7 +6468,7 @@
         <v>Promotional Materials Costs - Expense</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="str">
         <f>_xlfn.CONCAT(All!A46, " - Assets")</f>
         <v>Prepaid Security Services - Assets</v>
@@ -6403,7 +6482,7 @@
         <v>Water Fees - Expense</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="str">
         <f>_xlfn.CONCAT(All!A47, " - Assets")</f>
         <v>Prepaid Subscriptions - Assets</v>
@@ -6417,7 +6496,7 @@
         <v>Property Tax Fees - Expense</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="str">
         <f>_xlfn.CONCAT(All!A48, " - Assets")</f>
         <v>Raw Materials Inventory - Assets</v>
@@ -6431,7 +6510,7 @@
         <v>Purchase Allowances - Expense</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="str">
         <f>_xlfn.CONCAT(All!A49, " - Assets")</f>
         <v>Rent Receivable - Assets</v>
@@ -6445,7 +6524,7 @@
         <v>Purchases - Expense</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="str">
         <f>_xlfn.CONCAT(All!A50, " - Assets")</f>
         <v>Savings Accounts - Assets</v>
@@ -6459,7 +6538,7 @@
         <v>Purchases Discounts - Expense</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="str">
         <f>_xlfn.CONCAT(All!A51, " - Assets")</f>
         <v>Service Equipment - Assets</v>
@@ -6473,7 +6552,7 @@
         <v>Rent Fees - Expense</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="str">
         <f>_xlfn.CONCAT(All!A52, " - Assets")</f>
         <v>Short-Term Bonds Receivable - Assets</v>
@@ -6487,7 +6566,7 @@
         <v>Repairs &amp; Maintenance Costs - Expense</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="str">
         <f>_xlfn.CONCAT(All!A53, " - Assets")</f>
         <v>Supplies Inventory - Assets</v>
@@ -6501,7 +6580,7 @@
         <v>Research and Development Costs - Expense</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="str">
         <f>_xlfn.CONCAT(All!A54, " - Assets")</f>
         <v>Tax Refund Receivable - Assets</v>
@@ -6515,7 +6594,7 @@
         <v>Royalties Paid - Expense</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="str">
         <f>_xlfn.CONCAT(All!A55, " - Assets")</f>
         <v>Trademark - Assets</v>
@@ -6529,7 +6608,7 @@
         <v>Salaries Paid - Expense</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="str">
         <f>_xlfn.CONCAT(All!A56, " - Assets")</f>
         <v>Trading Securities - Assets</v>
@@ -6543,7 +6622,7 @@
         <v>Security Services Costs - Expense</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="str">
         <f>_xlfn.CONCAT(All!A57, " - Assets")</f>
         <v>Treasury Bills - Assets</v>
@@ -6557,7 +6636,7 @@
         <v>Service Charges - Expense</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="str">
         <f>_xlfn.CONCAT(All!A58, " - Assets")</f>
         <v>Trucks - Assets</v>
@@ -6567,7 +6646,7 @@
         <v>Service Supplies Costs - Expense</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="str">
         <f>_xlfn.CONCAT(All!A59, " - Assets")</f>
         <v>Work-in-Process Inventory - Assets</v>
@@ -6577,55 +6656,55 @@
         <v>Social Security Taxes Paid - Expense</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C61" s="2" t="str">
         <f>_xlfn.CONCAT(All!C57, " - Expense")</f>
         <v>Software Subscription Costs - Expense</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C62" s="2" t="str">
         <f>_xlfn.CONCAT(All!C58, " - Expense")</f>
         <v>Store Supplies Costs - Expense</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C63" s="4" t="str">
         <f>_xlfn.CONCAT(All!C59, " - Expense")</f>
         <v>Supplies Costs - Expense</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C64" s="3" t="str">
         <f>_xlfn.CONCAT(All!C60, " - Expense")</f>
         <v>Taxes Costs - Expense</v>
       </c>
     </row>
-    <row r="65" spans="3:3">
+    <row r="65" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C65" s="2" t="str">
         <f>_xlfn.CONCAT(All!C61, " - Expense")</f>
         <v>Trade Show Costs - Expense</v>
       </c>
     </row>
-    <row r="66" spans="3:3">
+    <row r="66" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C66" s="3" t="str">
         <f>_xlfn.CONCAT(All!C62, " - Expense")</f>
         <v>Training Costs - Expense</v>
       </c>
     </row>
-    <row r="67" spans="3:3">
+    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C67" s="3" t="str">
         <f>_xlfn.CONCAT(All!C63, " - Expense")</f>
         <v>Transportation-In - Expense</v>
       </c>
     </row>
-    <row r="68" spans="3:3">
+    <row r="68" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C68" s="3" t="str">
         <f>_xlfn.CONCAT(All!C64, " - Expense")</f>
         <v>Travel Costs - Expense</v>
       </c>
     </row>
-    <row r="69" spans="3:3">
+    <row r="69" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C69" s="3" t="str">
         <f>_xlfn.CONCAT(All!C65, " - Expense")</f>
         <v>Unemployment Taxes Costs - Expense</v>
@@ -6646,14 +6725,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="44.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6664,7 +6743,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -6675,7 +6754,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>45</v>
       </c>
@@ -6686,7 +6765,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
@@ -6697,7 +6776,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>50</v>
       </c>
@@ -6705,7 +6784,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>218</v>
       </c>
@@ -6713,7 +6792,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>65</v>
       </c>
@@ -6721,7 +6800,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>85</v>
       </c>
@@ -6729,7 +6808,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>95</v>
       </c>
@@ -6737,7 +6816,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>98</v>
       </c>
@@ -6745,7 +6824,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>101</v>
       </c>
@@ -6753,7 +6832,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>104</v>
       </c>
@@ -6761,7 +6840,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>110</v>
       </c>
@@ -6769,7 +6848,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>122</v>
       </c>
@@ -6777,7 +6856,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>128</v>
       </c>
@@ -6785,7 +6864,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>140</v>
       </c>
@@ -6793,7 +6872,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>143</v>
       </c>
@@ -6801,7 +6880,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>146</v>
       </c>
@@ -6809,7 +6888,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>152</v>
       </c>
@@ -6817,47 +6896,47 @@
         <v>198</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>203</v>
       </c>
@@ -6877,14 +6956,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="44.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6895,7 +6974,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -6906,7 +6985,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -6917,7 +6996,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -6928,7 +7007,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
@@ -6939,7 +7018,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
@@ -6950,7 +7029,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>45</v>
       </c>
@@ -6961,7 +7040,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>60</v>
       </c>
@@ -6972,7 +7051,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>69</v>
       </c>
@@ -6983,7 +7062,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>73</v>
       </c>
@@ -6994,7 +7073,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>77</v>
       </c>
@@ -7002,7 +7081,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>85</v>
       </c>
@@ -7010,7 +7089,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>89</v>
       </c>
@@ -7018,7 +7097,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>92</v>
       </c>
@@ -7026,7 +7105,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>98</v>
       </c>
@@ -7034,7 +7113,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>101</v>
       </c>
@@ -7042,7 +7121,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>104</v>
       </c>
@@ -7050,7 +7129,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>110</v>
       </c>
@@ -7058,7 +7137,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>122</v>
       </c>
@@ -7066,7 +7145,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>125</v>
       </c>
@@ -7074,7 +7153,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>134</v>
       </c>
@@ -7082,7 +7161,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>140</v>
       </c>
@@ -7090,7 +7169,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>143</v>
       </c>
@@ -7098,7 +7177,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>146</v>
       </c>
@@ -7106,7 +7185,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>149</v>
       </c>
@@ -7114,7 +7193,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>152</v>
       </c>
@@ -7122,7 +7201,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>155</v>
       </c>
@@ -7130,7 +7209,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>173</v>
       </c>
@@ -7138,7 +7217,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>179</v>
       </c>
@@ -7146,7 +7225,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>182</v>
       </c>
@@ -7154,7 +7233,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>185</v>
       </c>
@@ -7162,7 +7241,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>188</v>
       </c>
@@ -7170,7 +7249,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>194</v>
       </c>
@@ -7178,7 +7257,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>206</v>
       </c>
@@ -7186,27 +7265,27 @@
         <v>186</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
         <v>204</v>
       </c>
@@ -7226,14 +7305,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="44.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7244,7 +7323,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -7255,7 +7334,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -7266,7 +7345,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -7277,7 +7356,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
@@ -7288,7 +7367,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -7299,7 +7378,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>30</v>
       </c>
@@ -7310,7 +7389,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>35</v>
       </c>
@@ -7321,7 +7400,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>40</v>
       </c>
@@ -7332,7 +7411,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>45</v>
       </c>
@@ -7343,7 +7422,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>55</v>
       </c>
@@ -7354,7 +7433,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>73</v>
       </c>
@@ -7365,7 +7444,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>77</v>
       </c>
@@ -7376,7 +7455,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>81</v>
       </c>
@@ -7384,7 +7463,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>92</v>
       </c>
@@ -7392,7 +7471,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>98</v>
       </c>
@@ -7400,7 +7479,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>101</v>
       </c>
@@ -7408,7 +7487,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>107</v>
       </c>
@@ -7416,7 +7495,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>110</v>
       </c>
@@ -7424,7 +7503,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>113</v>
       </c>
@@ -7432,7 +7511,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>116</v>
       </c>
@@ -7440,7 +7519,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>119</v>
       </c>
@@ -7448,7 +7527,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>131</v>
       </c>
@@ -7456,7 +7535,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>137</v>
       </c>
@@ -7464,7 +7543,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>140</v>
       </c>
@@ -7472,7 +7551,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>143</v>
       </c>
@@ -7480,7 +7559,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>146</v>
       </c>
@@ -7488,7 +7567,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>155</v>
       </c>
@@ -7496,7 +7575,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>161</v>
       </c>
@@ -7504,7 +7583,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>170</v>
       </c>
@@ -7512,7 +7591,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>182</v>
       </c>
@@ -7520,7 +7599,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>191</v>
       </c>
@@ -7528,7 +7607,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>194</v>
       </c>
@@ -7536,7 +7615,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>197</v>
       </c>
@@ -7544,7 +7623,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>200</v>
       </c>
@@ -7552,7 +7631,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>204</v>
       </c>
@@ -7572,13 +7651,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -7586,7 +7665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>219</v>
       </c>
@@ -7594,7 +7673,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>221</v>
       </c>
@@ -7602,7 +7681,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -7610,7 +7689,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>42</v>
       </c>
@@ -7618,7 +7697,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>52</v>
       </c>
@@ -7626,112 +7705,112 @@
         <v>224</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -7751,13 +7830,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B43"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -7765,7 +7844,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>221</v>
       </c>
@@ -7773,7 +7852,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>219</v>
       </c>
@@ -7781,7 +7860,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -7789,7 +7868,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -7797,7 +7876,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
@@ -7805,7 +7884,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -7813,7 +7892,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>232</v>
       </c>
@@ -7821,7 +7900,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
@@ -7829,7 +7908,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>67</v>
       </c>
@@ -7837,7 +7916,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>71</v>
       </c>
@@ -7845,7 +7924,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>75</v>
       </c>
@@ -7853,7 +7932,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>79</v>
       </c>
@@ -7861,7 +7940,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>91</v>
       </c>
@@ -7869,7 +7948,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>234</v>
       </c>
@@ -7877,142 +7956,142 @@
         <v>224</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>214</v>
       </c>
@@ -8032,13 +8111,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B39"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -8046,7 +8125,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>133</v>
       </c>
@@ -8054,7 +8133,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>219</v>
       </c>
@@ -8062,7 +8141,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>221</v>
       </c>
@@ -8070,7 +8149,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -8078,7 +8157,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
@@ -8086,7 +8165,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -8094,7 +8173,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>47</v>
       </c>
@@ -8102,7 +8181,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>232</v>
       </c>
@@ -8110,7 +8189,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>62</v>
       </c>
@@ -8118,7 +8197,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>67</v>
       </c>
@@ -8126,7 +8205,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>71</v>
       </c>
@@ -8134,7 +8213,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>79</v>
       </c>
@@ -8142,7 +8221,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>83</v>
       </c>
@@ -8150,7 +8229,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>91</v>
       </c>
@@ -8158,7 +8237,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>100</v>
       </c>
@@ -8166,7 +8245,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>109</v>
       </c>
@@ -8174,7 +8253,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>112</v>
       </c>
@@ -8182,7 +8261,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>235</v>
       </c>
@@ -8190,7 +8269,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>124</v>
       </c>
@@ -8198,97 +8277,97 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>214</v>
       </c>
@@ -8305,13 +8384,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1924A69-9EA0-4A41-BBB2-9FB56813B04B}">
   <dimension ref="A1:B127"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>245</v>
       </c>
@@ -8319,7 +8398,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>247</v>
       </c>
@@ -8327,7 +8406,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -8335,7 +8414,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>248</v>
       </c>
@@ -8343,7 +8422,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>249</v>
       </c>
@@ -8351,7 +8430,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>250</v>
       </c>
@@ -8359,7 +8438,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>40</v>
       </c>
@@ -8367,7 +8446,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
@@ -8375,7 +8454,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>50</v>
       </c>
@@ -8383,7 +8462,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>218</v>
       </c>
@@ -8391,7 +8470,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>251</v>
       </c>
@@ -8399,7 +8478,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>65</v>
       </c>
@@ -8407,7 +8486,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>39</v>
       </c>
@@ -8415,7 +8494,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>252</v>
       </c>
@@ -8423,7 +8502,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>253</v>
       </c>
@@ -8431,7 +8510,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>85</v>
       </c>
@@ -8439,7 +8518,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>254</v>
       </c>
@@ -8447,7 +8526,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>95</v>
       </c>
@@ -8455,7 +8534,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>255</v>
       </c>
@@ -8463,7 +8542,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>98</v>
       </c>
@@ -8471,7 +8550,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>257</v>
       </c>
@@ -8479,7 +8558,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>258</v>
       </c>
@@ -8487,7 +8566,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>101</v>
       </c>
@@ -8495,7 +8574,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>104</v>
       </c>
@@ -8503,7 +8582,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>110</v>
       </c>
@@ -8511,7 +8590,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>122</v>
       </c>
@@ -8519,7 +8598,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>128</v>
       </c>
@@ -8527,7 +8606,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>261</v>
       </c>
@@ -8535,7 +8614,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>263</v>
       </c>
@@ -8543,7 +8622,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>264</v>
       </c>
@@ -8551,7 +8630,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>140</v>
       </c>
@@ -8559,7 +8638,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>143</v>
       </c>
@@ -8567,7 +8646,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>265</v>
       </c>
@@ -8575,7 +8654,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>266</v>
       </c>
@@ -8583,7 +8662,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>146</v>
       </c>
@@ -8591,7 +8670,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>267</v>
       </c>
@@ -8599,7 +8678,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>152</v>
       </c>
@@ -8607,7 +8686,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>155</v>
       </c>
@@ -8615,7 +8694,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>158</v>
       </c>
@@ -8623,7 +8702,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>161</v>
       </c>
@@ -8631,7 +8710,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>164</v>
       </c>
@@ -8639,7 +8718,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>167</v>
       </c>
@@ -8647,7 +8726,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>170</v>
       </c>
@@ -8655,7 +8734,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>176</v>
       </c>
@@ -8663,7 +8742,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>269</v>
       </c>
@@ -8671,7 +8750,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>270</v>
       </c>
@@ -8679,7 +8758,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>271</v>
       </c>
@@ -8687,7 +8766,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>272</v>
       </c>
@@ -8695,7 +8774,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>273</v>
       </c>
@@ -8703,7 +8782,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>274</v>
       </c>
@@ -8711,7 +8790,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>275</v>
       </c>
@@ -8719,7 +8798,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>203</v>
       </c>
@@ -8727,7 +8806,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>276</v>
       </c>
@@ -8735,7 +8814,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>277</v>
       </c>
@@ -8743,7 +8822,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>278</v>
       </c>
@@ -8751,7 +8830,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>279</v>
       </c>
@@ -8759,7 +8838,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>280</v>
       </c>
@@ -8767,7 +8846,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>281</v>
       </c>
@@ -8775,7 +8854,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>27</v>
       </c>
@@ -8783,7 +8862,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>282</v>
       </c>
@@ -8791,7 +8870,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>60</v>
       </c>
@@ -8799,7 +8878,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>284</v>
       </c>
@@ -8807,7 +8886,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>69</v>
       </c>
@@ -8815,7 +8894,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>285</v>
       </c>
@@ -8823,7 +8902,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>73</v>
       </c>
@@ -8831,7 +8910,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>67</v>
       </c>
@@ -8839,7 +8918,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>71</v>
       </c>
@@ -8847,7 +8926,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>77</v>
       </c>
@@ -8855,7 +8934,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>286</v>
       </c>
@@ -8863,7 +8942,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>287</v>
       </c>
@@ -8871,7 +8950,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>288</v>
       </c>
@@ -8879,7 +8958,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>89</v>
       </c>
@@ -8887,7 +8966,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>92</v>
       </c>
@@ -8895,7 +8974,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>289</v>
       </c>
@@ -8903,7 +8982,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>290</v>
       </c>
@@ -8911,7 +8990,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>291</v>
       </c>
@@ -8919,7 +8998,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>127</v>
       </c>
@@ -8927,7 +9006,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>130</v>
       </c>
@@ -8935,7 +9014,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>133</v>
       </c>
@@ -8943,7 +9022,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>292</v>
       </c>
@@ -8951,7 +9030,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>134</v>
       </c>
@@ -8959,7 +9038,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>294</v>
       </c>
@@ -8967,7 +9046,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>295</v>
       </c>
@@ -8975,7 +9054,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>149</v>
       </c>
@@ -8983,7 +9062,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>296</v>
       </c>
@@ -8991,7 +9070,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>297</v>
       </c>
@@ -8999,7 +9078,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>173</v>
       </c>
@@ -9007,7 +9086,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>298</v>
       </c>
@@ -9015,7 +9094,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>299</v>
       </c>
@@ -9023,7 +9102,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>80</v>
       </c>
@@ -9031,7 +9110,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>84</v>
       </c>
@@ -9039,7 +9118,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>179</v>
       </c>
@@ -9047,177 +9126,177 @@
         <v>88</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="103" spans="1:1">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="105" spans="1:1">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="108" spans="1:1">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:1">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:1">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="111" spans="1:1">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="112" spans="1:1">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="113" spans="1:1">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="114" spans="1:1">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="115" spans="1:1">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="116" spans="1:1">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="117" spans="1:1">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="118" spans="1:1">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="119" spans="1:1">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="120" spans="1:1">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="121" spans="1:1">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="122" spans="1:1">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="123" spans="1:1">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="124" spans="1:1">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="125" spans="1:1">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="127" spans="1:1">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
         <v>64</v>
       </c>
@@ -9466,13 +9545,38 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8548443D-DC83-441E-A117-A889C06CA291}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8548443D-DC83-441E-A117-A889C06CA291}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75253D14-554A-4916-839F-E7F866211CA3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75253D14-554A-4916-839F-E7F866211CA3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="47b4e388-7a75-40af-8b04-42818f2fdb9b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA3D524E-4D0B-4E73-9423-303FE9996AF8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA3D524E-4D0B-4E73-9423-303FE9996AF8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="47b4e388-7a75-40af-8b04-42818f2fdb9b"/>
+    <ds:schemaRef ds:uri="c997e9c3-07ef-4103-ac9e-c49d1d746bce"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>